--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T20:00:37+00:00</t>
+    <t>2022-02-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-19T15:25:03+00:00</t>
+    <t>2022-05-23T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-23T06:59:28+00:00</t>
+    <t>2022-05-24T18:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-24T18:54:59+00:00</t>
+    <t>2022-08-17T21:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -819,43 +819,43 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.65625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.2734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.2578125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.44140625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="46.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="46.04296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.265625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.16796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.64453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="22.71484375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.2109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="18.18359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.55078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.87109375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="36" max="36" width="62.87890625" customWidth="true" bestFit="true"/>
     <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="25.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-17T21:15:17+00:00</t>
+    <t>2022-09-06T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T15:19:36+00:00</t>
+    <t>2022-09-06T18:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T18:47:55+00:00</t>
+    <t>2022-09-06T19:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:01:15+00:00</t>
+    <t>2022-09-06T19:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:02:52+00:00</t>
+    <t>2022-09-06T19:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:21:39+00:00</t>
+    <t>2022-09-13T07:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-13T07:22:16+00:00</t>
+    <t>2022-09-17T09:48:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:48:15+00:00</t>
+    <t>2022-09-17T09:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:59:31+00:00</t>
+    <t>2022-09-17T10:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T10:02:16+00:00</t>
+    <t>2022-10-04T11:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -259,107 +259,107 @@
 </t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
+    <t>Identifier.id</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Identifier.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>Identifier.id</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Identifier.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>official</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1068,13 +1068,13 @@
         <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AJ2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>30</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1093,25 +1093,25 @@
         <v>76</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="L3" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1162,13 +1162,13 @@
         <v>75</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>75</v>
@@ -1180,7 +1180,7 @@
         <v>75</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>75</v>
@@ -1188,11 +1188,11 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" t="s" s="2">
@@ -1211,16 +1211,16 @@
         <v>75</v>
       </c>
       <c r="J4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" t="s" s="2">
@@ -1258,19 +1258,19 @@
         <v>75</v>
       </c>
       <c r="AA4" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AB4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AB4" t="s" s="2">
+      <c r="AC4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AC4" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD4" t="s" s="2">
+      <c r="AE4" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="AF4" t="s" s="2">
         <v>76</v>
@@ -1282,13 +1282,13 @@
         <v>75</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -1307,63 +1307,63 @@
         <v>76</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="J5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="I5" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J5" t="s" s="2">
+      <c r="K5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="R5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="R5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W5" t="s" s="2">
+      <c r="X5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="X5" t="s" s="2">
+      <c r="Y5" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y5" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="Z5" t="s" s="2">
         <v>75</v>
       </c>
@@ -1380,19 +1380,19 @@
         <v>75</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>113</v>
@@ -1417,7 +1417,7 @@
         <v>76</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>75</v>
@@ -1426,7 +1426,7 @@
         <v>75</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J6" t="s" s="2">
         <v>116</v>
@@ -1496,13 +1496,13 @@
         <v>76</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>124</v>
@@ -1524,10 +1524,10 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>75</v>
@@ -1536,7 +1536,7 @@
         <v>75</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J7" t="s" s="2">
         <v>126</v>
@@ -1606,13 +1606,13 @@
         <v>76</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>133</v>
@@ -1634,22 +1634,22 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="J8" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>137</v>
@@ -1714,7 +1714,7 @@
         <v>76</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>75</v>
@@ -1745,7 +1745,7 @@
         <v>76</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>75</v>
@@ -1754,7 +1754,7 @@
         <v>75</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J9" t="s" s="2">
         <v>146</v>
@@ -1820,13 +1820,13 @@
         <v>76</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>149</v>
@@ -1851,7 +1851,7 @@
         <v>76</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>75</v>
@@ -1860,7 +1860,7 @@
         <v>75</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>153</v>
@@ -1928,13 +1928,13 @@
         <v>76</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>157</v>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T09:15:32+00:00</t>
+    <t>2023-04-18T12:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,6 +126,9 @@
     <t>constraint</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Path</t>
   </si>
   <si>
@@ -247,6 +250,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
   <si>
     <t>An identifier intended for computation</t>
@@ -815,47 +822,47 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="12.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="46.04296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="167.43359375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="36" max="36" width="62.87890625" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="25.4375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="62.87890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="143.74609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -973,977 +980,1007 @@
       <c r="AL1" t="s" s="1">
         <v>74</v>
       </c>
+      <c r="AM1" t="s" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="M2" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="M2" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="N2" s="2"/>
-      <c r="O2" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" t="s" s="2">
-        <v>75</v>
-      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AF2" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF3" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L3" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AI3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>75</v>
+        <v>91</v>
+      </c>
+      <c r="AM3" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>75</v>
+        <v>91</v>
+      </c>
+      <c r="AM4" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O5" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="P5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="K5" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="R5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AG5" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
+      </c>
+      <c r="AM5" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="P6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AL6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="K6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="O6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W6" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="X6" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>75</v>
+      <c r="AM6" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="O7" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF7" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="R7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S7" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="T7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD7" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AG7" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M8" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AG8" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AG9" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>153</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="R10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="AG10" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,6 +266,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
@@ -365,10 +369,6 @@
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -456,15 +456,15 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-CVR-length:CVR must be exactly 8 numeric characters long {value.matches('^[0-9]{8}$')}CVR-modulus-11:CVR must pass the modulus 11 check {((
-    (value.substring(0,1).toInteger()*2)+
-    (value.substring(1,1).toInteger()*7)+
-    (value.substring(2,1).toInteger()*6)+
-    (value.substring(3,1).toInteger()*5)+
-    (value.substring(4,1).toInteger()*4)+
-    (value.substring(5,1).toInteger()*3)+
-    (value.substring(6,1).toInteger()*2)+
-    (value.substring(7,1).toInteger()*1)) mod(11)=0)}</t>
+CVR-length:CVR must be exactly 8 numeric characters long {matches('^[0-9]{8}$')}CVR-modulus-11:CVR must pass the modulus 11 check {((
+    (substring(0,1).toInteger()*2)+
+    (substring(1,1).toInteger()*7)+
+    (substring(2,1).toInteger()*6)+
+    (substring(3,1).toInteger()*5)+
+    (substring(4,1).toInteger()*4)+
+    (substring(5,1).toInteger()*3)+
+    (substring(6,1).toInteger()*2)+
+    (substring(7,1).toInteger()*1)) mod(11)=0)}</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -642,10 +642,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1081,13 +1081,13 @@
         <v>82</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>30</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1109,7 +1109,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1121,13 +1121,13 @@
         <v>76</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1178,13 +1178,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1196,7 +1196,7 @@
         <v>76</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM3" t="s" s="2">
         <v>76</v>
@@ -1204,14 +1204,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1230,16 +1230,16 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1277,19 +1277,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1301,13 +1301,13 @@
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>76</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1329,38 +1329,38 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="S5" t="s" s="2">
         <v>76</v>
@@ -1378,13 +1378,13 @@
         <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>76</v>
@@ -1402,19 +1402,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>115</v>
@@ -1442,7 +1442,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1451,7 +1451,7 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s" s="2">
         <v>118</v>
@@ -1521,13 +1521,13 @@
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>126</v>
@@ -1552,10 +1552,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -1564,7 +1564,7 @@
         <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K7" t="s" s="2">
         <v>128</v>
@@ -1634,13 +1634,13 @@
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>135</v>
@@ -1665,10 +1665,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>76</v>
@@ -1677,10 +1677,10 @@
         <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
         <v>139</v>
@@ -1745,7 +1745,7 @@
         <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>76</v>
@@ -1779,7 +1779,7 @@
         <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>76</v>
@@ -1788,7 +1788,7 @@
         <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>148</v>
@@ -1854,13 +1854,13 @@
         <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>151</v>
@@ -1888,7 +1888,7 @@
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>76</v>
@@ -1897,7 +1897,7 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>155</v>
@@ -1965,13 +1965,13 @@
         <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>159</v>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-cvr-identifier.xlsx
+++ b/StructureDefinition-dk-core-cvr-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
